--- a/backend/excel-templates/test-data/bachelor_upload_test_data.xlsx
+++ b/backend/excel-templates/test-data/bachelor_upload_test_data.xlsx
@@ -398,6 +398,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G31"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="45.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,19 +416,19 @@
         <v>Project Title</v>
       </c>
       <c r="C1" t="str">
-        <v>Member Names</v>
+        <v>Members</v>
       </c>
       <c r="D1" t="str">
         <v>Roll Numbers</v>
       </c>
       <c r="E1" t="str">
-        <v>Academic Year</v>
+        <v>Batch</v>
       </c>
       <c r="F1" t="str">
         <v>Supervisor</v>
       </c>
       <c r="G1" t="str">
-        <v>Examiner</v>
+        <v>External Examiner</v>
       </c>
     </row>
     <row r="2">
@@ -427,22 +436,22 @@
         <v>TestGroup_1</v>
       </c>
       <c r="B2" t="str">
-        <v>Test Bachelor Project 1 — IoT Application</v>
+        <v>Test Bachelor Project 1 — ML Application</v>
       </c>
       <c r="C2" t="str">
-        <v>Ram Acharya, Shyam Basnet, Hari Chhetri</v>
+        <v>Sita Dahal, Gita Gurung, Rita Khadka</v>
       </c>
       <c r="D2" t="str">
-        <v>078BCT001, 078BEI002, 078BCT003</v>
+        <v>78BCT004, 78BEI003, 78BCT013</v>
       </c>
       <c r="E2" t="str">
-        <v>2081</v>
+        <v>78</v>
       </c>
       <c r="F2" t="str">
-        <v>Dr. Ram Acharya</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="G2" t="str">
-        <v>Prof. Hari Bhandari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="3">
@@ -450,22 +459,22 @@
         <v>TestGroup_2</v>
       </c>
       <c r="B3" t="str">
-        <v>Test Bachelor Project 2 — ML Application</v>
+        <v>Test Bachelor Project 2 — Web Application</v>
       </c>
       <c r="C3" t="str">
-        <v>Sita Dahal, Gita Gurung, Rita Khadka</v>
+        <v>Krishna Lama, Bishnu Maharjan, Arjun Neupane</v>
       </c>
       <c r="D3" t="str">
-        <v>078BEI004, 078BCT005, 078BEI006</v>
+        <v>78BCT007, 78BEI005, 78BCT018</v>
       </c>
       <c r="E3" t="str">
-        <v>2081</v>
+        <v>78</v>
       </c>
       <c r="F3" t="str">
-        <v>Prof. Sita Sharma</v>
+        <v>Assoc. Prof. Krishna Poudel</v>
       </c>
       <c r="G3" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="4">
@@ -473,22 +482,22 @@
         <v>TestGroup_3</v>
       </c>
       <c r="B4" t="str">
-        <v>Test Bachelor Project 3 — Web Application</v>
+        <v>Test Bachelor Project 3 — Mobile Application</v>
       </c>
       <c r="C4" t="str">
-        <v>Krishna Lama, Bishnu Maharjan, Arjun Neupane</v>
+        <v>Pooja Pandey, Rajan Shrestha, Nisha Thapa</v>
       </c>
       <c r="D4" t="str">
-        <v>078BCT007, 078BEI008, 078BCT009</v>
+        <v>78BCT010, 78BEI007, 78BCT023</v>
       </c>
       <c r="E4" t="str">
-        <v>2081</v>
+        <v>78</v>
       </c>
       <c r="F4" t="str">
-        <v>Assoc. Prof. Krishna Poudel</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="G4" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="5">
@@ -496,22 +505,22 @@
         <v>TestGroup_4</v>
       </c>
       <c r="B5" t="str">
-        <v>Test Bachelor Project 4 — Mobile Application</v>
+        <v>Test Bachelor Project 4 — AI Application</v>
       </c>
       <c r="C5" t="str">
-        <v>Pratik Ojha, Nabin Pandey, Sagar Rai</v>
+        <v>Bibek Poudel, Muna Rai, Dipesh Khatri</v>
       </c>
       <c r="D5" t="str">
-        <v>078BEI010, 078BCT011, 078BEI012</v>
+        <v>78BCT013, 78BEI009, 78BCT028</v>
       </c>
       <c r="E5" t="str">
-        <v>2081</v>
+        <v>78</v>
       </c>
       <c r="F5" t="str">
-        <v>Dr. Gita Rai</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="G5" t="str">
-        <v>Dr. Umesh Lama</v>
+        <v>Prof. Hari Bhandari</v>
       </c>
     </row>
     <row r="6">
@@ -522,19 +531,19 @@
         <v>Test Bachelor Project 5 — Blockchain Application</v>
       </c>
       <c r="C6" t="str">
-        <v>Roshan Sharma, Bibek Thapa, Amit Poudel</v>
+        <v>Kabita Joshi, Yubaraj Karki, Sarita Adhikari</v>
       </c>
       <c r="D6" t="str">
-        <v>078BCT013, 078BEI014, 078BCT015</v>
+        <v>78BCT016, 78BEI011, 78BCT033</v>
       </c>
       <c r="E6" t="str">
-        <v>2081</v>
+        <v>78</v>
       </c>
       <c r="F6" t="str">
-        <v>Prof. Mohan Adhikari</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="G6" t="str">
-        <v>Prof. Sunita Acharya</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="7">
@@ -542,22 +551,22 @@
         <v>TestGroup_6</v>
       </c>
       <c r="B7" t="str">
-        <v>Test Bachelor Project 6 — NLP Application</v>
+        <v>Test Bachelor Project 6 — Security Application</v>
       </c>
       <c r="C7" t="str">
-        <v>Sunita Pokhrel, Kabita Adhikari, Pooja Bhandari</v>
+        <v>Nabin Bista, Reema Pathak, Anup Ghimire</v>
       </c>
       <c r="D7" t="str">
-        <v>078BEI016, 078BCT017, 078BEI018</v>
+        <v>78BCT019, 78BEI013, 78BCT038</v>
       </c>
       <c r="E7" t="str">
-        <v>2081</v>
+        <v>78</v>
       </c>
       <c r="F7" t="str">
-        <v>Dr. Bishnu Basnet</v>
+        <v>Assoc. Prof. Krishna Poudel</v>
       </c>
       <c r="G7" t="str">
-        <v>Dr. Roshan Karki</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="8">
@@ -565,22 +574,22 @@
         <v>TestGroup_7</v>
       </c>
       <c r="B8" t="str">
-        <v>Test Bachelor Project 7 — CV Application</v>
+        <v>Test Bachelor Project 7 — Cloud Application</v>
       </c>
       <c r="C8" t="str">
-        <v>Anita Acharya, Sarita Basnet, Deepak Chhetri</v>
+        <v>Bhawana Bastola, Dinesh Baral, Elina Pokharel</v>
       </c>
       <c r="D8" t="str">
-        <v>078BCT019, 078BEI020, 078BCT021</v>
+        <v>78BCT022, 78BEI015, 78BCT043</v>
       </c>
       <c r="E8" t="str">
-        <v>2081</v>
+        <v>78</v>
       </c>
       <c r="F8" t="str">
-        <v>Dr. Ram Acharya</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="G8" t="str">
-        <v>Prof. Hari Bhandari</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="9">
@@ -588,22 +597,22 @@
         <v>TestGroup_8</v>
       </c>
       <c r="B9" t="str">
-        <v>Test Bachelor Project 8 — Robotics Application</v>
+        <v>Test Bachelor Project 8 — IoT Application</v>
       </c>
       <c r="C9" t="str">
-        <v>Mohan Dahal, Rajan Gurung, Umesh Khadka</v>
+        <v>Ram Acharya, Shyam Basnet, Hari Chhetri</v>
       </c>
       <c r="D9" t="str">
-        <v>078BEI022, 078BCT023, 078BEI024</v>
+        <v>79BCT025, 79BEI017, 79BCT048</v>
       </c>
       <c r="E9" t="str">
-        <v>2081</v>
+        <v>79</v>
       </c>
       <c r="F9" t="str">
-        <v>Prof. Sita Sharma</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="G9" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Prof. Hari Bhandari</v>
       </c>
     </row>
     <row r="10">
@@ -611,22 +620,22 @@
         <v>TestGroup_9</v>
       </c>
       <c r="B10" t="str">
-        <v>Test Bachelor Project 9 — Embedded Application</v>
+        <v>Test Bachelor Project 9 — ML Application</v>
       </c>
       <c r="C10" t="str">
-        <v>Prakash Lama, Mina Maharjan, Tara Neupane</v>
+        <v>Sita Dahal, Gita Gurung, Rita Khadka</v>
       </c>
       <c r="D10" t="str">
-        <v>078BCT025, 078BEI026, 078BCT027</v>
+        <v>79BCT028, 79BEI019, 79BCT053</v>
       </c>
       <c r="E10" t="str">
-        <v>2081</v>
+        <v>79</v>
       </c>
       <c r="F10" t="str">
-        <v>Assoc. Prof. Krishna Poudel</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="G10" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="11">
@@ -634,22 +643,22 @@
         <v>TestGroup_10</v>
       </c>
       <c r="B11" t="str">
-        <v>Test Bachelor Project 10 — Cloud Application</v>
+        <v>Test Bachelor Project 10 — Web Application</v>
       </c>
       <c r="C11" t="str">
-        <v>Reema Ojha, Sushma Pandey, Anjana Rai</v>
+        <v>Krishna Lama, Bishnu Maharjan, Arjun Neupane</v>
       </c>
       <c r="D11" t="str">
-        <v>078BEI028, 078BCT029, 078BEI030</v>
+        <v>79BCT031, 79BEI021, 79BCT058</v>
       </c>
       <c r="E11" t="str">
-        <v>2081</v>
+        <v>79</v>
       </c>
       <c r="F11" t="str">
-        <v>Dr. Gita Rai</v>
+        <v>Assoc. Prof. Krishna Poudel</v>
       </c>
       <c r="G11" t="str">
-        <v>Dr. Umesh Lama</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="12">
@@ -657,22 +666,22 @@
         <v>TestGroup_11</v>
       </c>
       <c r="B12" t="str">
-        <v>Test Bachelor Project 11 — IoT Application</v>
+        <v>Test Bachelor Project 11 — Mobile Application</v>
       </c>
       <c r="C12" t="str">
-        <v>Ram Sharma, Shyam Thapa, Hari Poudel</v>
+        <v>Pooja Pandey, Rajan Shrestha, Nisha Thapa</v>
       </c>
       <c r="D12" t="str">
-        <v>078BCT031, 078BEI032, 078BCT033</v>
+        <v>79BCT034, 79BEI023, 79BCT063</v>
       </c>
       <c r="E12" t="str">
-        <v>2081</v>
+        <v>79</v>
       </c>
       <c r="F12" t="str">
-        <v>Prof. Mohan Adhikari</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="G12" t="str">
-        <v>Prof. Sunita Acharya</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="13">
@@ -680,22 +689,22 @@
         <v>TestGroup_12</v>
       </c>
       <c r="B13" t="str">
-        <v>Test Bachelor Project 12 — ML Application</v>
+        <v>Test Bachelor Project 12 — AI Application</v>
       </c>
       <c r="C13" t="str">
-        <v>Sita Pokhrel, Gita Adhikari, Rita Bhandari</v>
+        <v>Bibek Poudel, Muna Rai, Dipesh Khatri</v>
       </c>
       <c r="D13" t="str">
-        <v>078BEI034, 078BCT035, 078BEI036</v>
+        <v>79BCT037, 79BEI025, 79BCT068</v>
       </c>
       <c r="E13" t="str">
-        <v>2081</v>
+        <v>79</v>
       </c>
       <c r="F13" t="str">
-        <v>Dr. Bishnu Basnet</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="G13" t="str">
-        <v>Dr. Roshan Karki</v>
+        <v>Prof. Hari Bhandari</v>
       </c>
     </row>
     <row r="14">
@@ -703,22 +712,22 @@
         <v>TestGroup_13</v>
       </c>
       <c r="B14" t="str">
-        <v>Test Bachelor Project 13 — Web Application</v>
+        <v>Test Bachelor Project 13 — Blockchain Application</v>
       </c>
       <c r="C14" t="str">
-        <v>Krishna Acharya, Bishnu Basnet, Arjun Chhetri</v>
+        <v>Kabita Joshi, Yubaraj Karki, Sarita Adhikari</v>
       </c>
       <c r="D14" t="str">
-        <v>078BCT037, 078BEI038, 078BCT039</v>
+        <v>79BCT040, 79BEI027, 79BCT073</v>
       </c>
       <c r="E14" t="str">
-        <v>2081</v>
+        <v>79</v>
       </c>
       <c r="F14" t="str">
-        <v>Dr. Ram Acharya</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="G14" t="str">
-        <v>Prof. Hari Bhandari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="15">
@@ -726,22 +735,22 @@
         <v>TestGroup_14</v>
       </c>
       <c r="B15" t="str">
-        <v>Test Bachelor Project 14 — Mobile Application</v>
+        <v>Test Bachelor Project 14 — Security Application</v>
       </c>
       <c r="C15" t="str">
-        <v>Pratik Dahal, Nabin Gurung, Sagar Khadka</v>
+        <v>Nabin Bista, Reema Pathak, Anup Ghimire</v>
       </c>
       <c r="D15" t="str">
-        <v>078BEI040, 078BCT041, 078BEI042</v>
+        <v>79BCT043, 79BEI029, 79BCT078</v>
       </c>
       <c r="E15" t="str">
-        <v>2081</v>
+        <v>79</v>
       </c>
       <c r="F15" t="str">
-        <v>Prof. Sita Sharma</v>
+        <v>Assoc. Prof. Krishna Poudel</v>
       </c>
       <c r="G15" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="16">
@@ -749,22 +758,22 @@
         <v>TestGroup_15</v>
       </c>
       <c r="B16" t="str">
-        <v>Test Bachelor Project 15 — Blockchain Application</v>
+        <v>Test Bachelor Project 15 — Cloud Application</v>
       </c>
       <c r="C16" t="str">
-        <v>Roshan Lama, Bibek Maharjan, Amit Neupane</v>
+        <v>Bhawana Bastola, Dinesh Baral, Elina Pokharel</v>
       </c>
       <c r="D16" t="str">
-        <v>078BCT043, 078BEI044, 078BCT045</v>
+        <v>79BCT046, 79BEI031, 79BCT083</v>
       </c>
       <c r="E16" t="str">
-        <v>2081</v>
+        <v>79</v>
       </c>
       <c r="F16" t="str">
-        <v>Assoc. Prof. Krishna Poudel</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="G16" t="str">
-        <v>Assoc. Prof. Rita Maharjan</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="17">
@@ -772,22 +781,22 @@
         <v>TestGroup_16</v>
       </c>
       <c r="B17" t="str">
-        <v>Test Bachelor Project 16 — NLP Application</v>
+        <v>Test Bachelor Project 16 — IoT Application</v>
       </c>
       <c r="C17" t="str">
-        <v>Sunita Ojha, Kabita Pandey, Pooja Rai</v>
+        <v>Ram Acharya, Shyam Basnet, Hari Chhetri</v>
       </c>
       <c r="D17" t="str">
-        <v>078BEI046, 078BCT047, 078BEI048</v>
+        <v>80BCT049, 80BEI033, 80BCT088</v>
       </c>
       <c r="E17" t="str">
-        <v>2081</v>
+        <v>80</v>
       </c>
       <c r="F17" t="str">
-        <v>Dr. Gita Rai</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="G17" t="str">
-        <v>Dr. Umesh Lama</v>
+        <v>Prof. Hari Bhandari</v>
       </c>
     </row>
     <row r="18">
@@ -795,22 +804,22 @@
         <v>TestGroup_17</v>
       </c>
       <c r="B18" t="str">
-        <v>Test Bachelor Project 17 — CV Application</v>
+        <v>Test Bachelor Project 17 — ML Application</v>
       </c>
       <c r="C18" t="str">
-        <v>Anita Sharma, Sarita Thapa, Deepak Poudel</v>
+        <v>Sita Dahal, Gita Gurung, Rita Khadka</v>
       </c>
       <c r="D18" t="str">
-        <v>078BCT049, 078BEI050, 078BCT051</v>
+        <v>80BCT052, 80BEI035, 80BCT093</v>
       </c>
       <c r="E18" t="str">
-        <v>2081</v>
+        <v>80</v>
       </c>
       <c r="F18" t="str">
-        <v>Prof. Mohan Adhikari</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="G18" t="str">
-        <v>Prof. Sunita Acharya</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="19">
@@ -818,22 +827,22 @@
         <v>TestGroup_18</v>
       </c>
       <c r="B19" t="str">
-        <v>Test Bachelor Project 18 — Robotics Application</v>
+        <v>Test Bachelor Project 18 — Web Application</v>
       </c>
       <c r="C19" t="str">
-        <v>Mohan Pokhrel, Rajan Adhikari, Umesh Bhandari</v>
+        <v>Krishna Lama, Bishnu Maharjan, Arjun Neupane</v>
       </c>
       <c r="D19" t="str">
-        <v>078BEI052, 078BCT053, 078BEI054</v>
+        <v>80BCT055, 80BEI037, 80BCT002</v>
       </c>
       <c r="E19" t="str">
-        <v>2081</v>
+        <v>80</v>
       </c>
       <c r="F19" t="str">
-        <v>Dr. Bishnu Basnet</v>
+        <v>Assoc. Prof. Krishna Poudel</v>
       </c>
       <c r="G19" t="str">
-        <v>Dr. Roshan Karki</v>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="20">
@@ -841,22 +850,22 @@
         <v>TestGroup_19</v>
       </c>
       <c r="B20" t="str">
-        <v>Test Bachelor Project 19 — Embedded Application</v>
+        <v>Test Bachelor Project 19 — Mobile Application</v>
       </c>
       <c r="C20" t="str">
-        <v>Prakash Acharya, Mina Basnet, Tara Chhetri</v>
+        <v>Pooja Pandey, Rajan Shrestha, Nisha Thapa</v>
       </c>
       <c r="D20" t="str">
-        <v>078BCT055, 078BEI056, 078BCT057</v>
+        <v>80BCT058, 80BEI039, 80BCT007</v>
       </c>
       <c r="E20" t="str">
-        <v>2081</v>
+        <v>80</v>
       </c>
       <c r="F20" t="str">
-        <v>Dr. Ram Acharya</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="G20" t="str">
-        <v>Prof. Hari Bhandari</v>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="21">
@@ -864,22 +873,22 @@
         <v>TestGroup_20</v>
       </c>
       <c r="B21" t="str">
-        <v>Test Bachelor Project 20 — Cloud Application</v>
+        <v>Test Bachelor Project 20 — AI Application</v>
       </c>
       <c r="C21" t="str">
-        <v>Reema Dahal, Sushma Gurung, Anjana Khadka</v>
+        <v>Bibek Poudel, Muna Rai, Dipesh Khatri</v>
       </c>
       <c r="D21" t="str">
-        <v>078BEI058, 078BCT059, 078BEI060</v>
+        <v>80BCT061, 80BEI041, 80BCT012</v>
       </c>
       <c r="E21" t="str">
-        <v>2081</v>
+        <v>80</v>
       </c>
       <c r="F21" t="str">
-        <v>Prof. Sita Sharma</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="G21" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Prof. Hari Bhandari</v>
       </c>
     </row>
     <row r="22">
@@ -887,22 +896,22 @@
         <v>TestGroup_21</v>
       </c>
       <c r="B22" t="str">
-        <v>Test Bachelor Project 21 — IoT Application</v>
+        <v>Test Bachelor Project 21 — Blockchain Application</v>
       </c>
       <c r="C22" t="str">
-        <v>Ram Lama, Shyam Maharjan, Hari Neupane</v>
+        <v>Kabita Joshi, Yubaraj Karki, Sarita Adhikari</v>
       </c>
       <c r="D22" t="str">
-        <v>078BCT061, 078BEI062, 078BCT063</v>
+        <v>80BCT064, 80BEI043, 80BCT017</v>
       </c>
       <c r="E22" t="str">
-        <v>2081</v>
+        <v>80</v>
       </c>
       <c r="F22" t="str">
-        <v>Assoc. Prof. Krishna Poudel</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="23">
@@ -910,22 +919,22 @@
         <v>TestGroup_22</v>
       </c>
       <c r="B23" t="str">
-        <v>Test Bachelor Project 22 — ML Application</v>
+        <v>Test Bachelor Project 22 — Security Application</v>
       </c>
       <c r="C23" t="str">
-        <v>Sita Ojha, Gita Pandey, Rita Rai</v>
+        <v>Nabin Bista, Reema Pathak, Anup Ghimire</v>
       </c>
       <c r="D23" t="str">
-        <v>078BEI064, 078BCT065, 078BEI066</v>
+        <v>80BCT067, 80BEI045, 80BCT022</v>
       </c>
       <c r="E23" t="str">
-        <v>2081</v>
+        <v>80</v>
       </c>
       <c r="F23" t="str">
-        <v>Dr. Gita Rai</v>
+        <v>Assoc. Prof. Krishna Poudel</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="24">
@@ -933,22 +942,22 @@
         <v>TestGroup_23</v>
       </c>
       <c r="B24" t="str">
-        <v>Test Bachelor Project 23 — Web Application</v>
+        <v>Test Bachelor Project 23 — Cloud Application</v>
       </c>
       <c r="C24" t="str">
-        <v>Krishna Sharma, Bishnu Thapa, Arjun Poudel</v>
+        <v>Bhawana Bastola, Dinesh Baral, Elina Pokharel</v>
       </c>
       <c r="D24" t="str">
-        <v>078BCT067, 078BEI068, 078BCT069</v>
+        <v>80BCT070, 80BEI047, 80BCT027</v>
       </c>
       <c r="E24" t="str">
-        <v>2081</v>
+        <v>80</v>
       </c>
       <c r="F24" t="str">
-        <v>Prof. Mohan Adhikari</v>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="25">
@@ -956,22 +965,22 @@
         <v>TestGroup_24</v>
       </c>
       <c r="B25" t="str">
-        <v>Test Bachelor Project 24 — Mobile Application</v>
+        <v>Test Bachelor Project 24 — IoT Application</v>
       </c>
       <c r="C25" t="str">
-        <v>Pratik Pokhrel, Nabin Adhikari, Sagar Bhandari</v>
+        <v>Ram Acharya, Shyam Basnet, Hari Chhetri</v>
       </c>
       <c r="D25" t="str">
-        <v>078BEI070, 078BCT071, 078BEI072</v>
+        <v>81BCT073, 81BEI001, 81BCT032</v>
       </c>
       <c r="E25" t="str">
-        <v>2081</v>
+        <v>81</v>
       </c>
       <c r="F25" t="str">
-        <v>Dr. Bishnu Basnet</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>Prof. Hari Bhandari</v>
       </c>
     </row>
     <row r="26">
@@ -979,22 +988,22 @@
         <v>TestGroup_25</v>
       </c>
       <c r="B26" t="str">
-        <v>Test Bachelor Project 25 — Blockchain Application</v>
+        <v>Test Bachelor Project 25 — ML Application</v>
       </c>
       <c r="C26" t="str">
-        <v>Roshan Acharya, Bibek Basnet, Amit Chhetri</v>
+        <v>Sita Dahal, Gita Gurung, Rita Khadka</v>
       </c>
       <c r="D26" t="str">
-        <v>078BCT073, 078BEI074, 078BCT075</v>
+        <v>81BCT076, 81BEI003, 81BCT037</v>
       </c>
       <c r="E26" t="str">
-        <v>2081</v>
+        <v>81</v>
       </c>
       <c r="F26" t="str">
-        <v>Dr. Ram Acharya</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="27">
@@ -1002,22 +1011,22 @@
         <v>TestGroup_26</v>
       </c>
       <c r="B27" t="str">
-        <v>Test Bachelor Project 26 — NLP Application</v>
+        <v>Test Bachelor Project 26 — Web Application</v>
       </c>
       <c r="C27" t="str">
-        <v>Sunita Dahal, Kabita Gurung, Pooja Khadka</v>
+        <v>Krishna Lama, Bishnu Maharjan, Arjun Neupane</v>
       </c>
       <c r="D27" t="str">
-        <v>078BEI076, 078BCT077, 078BEI078</v>
+        <v>81BCT079, 81BEI005, 81BCT042</v>
       </c>
       <c r="E27" t="str">
-        <v>2081</v>
+        <v>81</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>Assoc. Prof. Krishna Poudel</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
     <row r="28">
@@ -1025,22 +1034,22 @@
         <v>TestGroup_27</v>
       </c>
       <c r="B28" t="str">
-        <v>Test Bachelor Project 27 — CV Application</v>
+        <v>Test Bachelor Project 27 — Mobile Application</v>
       </c>
       <c r="C28" t="str">
-        <v>Anita Lama, Sarita Maharjan, Deepak Neupane</v>
+        <v>Pooja Pandey, Rajan Shrestha, Nisha Thapa</v>
       </c>
       <c r="D28" t="str">
-        <v>078BCT079, 078BEI080, 078BCT081</v>
+        <v>81BCT082, 81BEI007, 81BCT047</v>
       </c>
       <c r="E28" t="str">
-        <v>2081</v>
+        <v>81</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>Dr. Pramod Acharya</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>Prof. Rajan Sharma</v>
       </c>
     </row>
     <row r="29">
@@ -1048,22 +1057,22 @@
         <v>TestGroup_28</v>
       </c>
       <c r="B29" t="str">
-        <v>Test Bachelor Project 28 — Robotics Application</v>
+        <v>Test Bachelor Project 28 — AI Application</v>
       </c>
       <c r="C29" t="str">
-        <v>Mohan Ojha, Rajan Pandey, Umesh Rai</v>
+        <v>Bibek Poudel, Muna Rai, Dipesh Khatri</v>
       </c>
       <c r="D29" t="str">
-        <v>078BEI082, 078BCT083, 078BEI084</v>
+        <v>81BCT085, 81BEI009, 81BCT052</v>
       </c>
       <c r="E29" t="str">
-        <v>2081</v>
+        <v>81</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>Prof. Hari Bhandari</v>
       </c>
     </row>
     <row r="30">
@@ -1071,22 +1080,22 @@
         <v>TestGroup_29</v>
       </c>
       <c r="B30" t="str">
-        <v>Test Bachelor Project 29 — Embedded Application</v>
+        <v>Test Bachelor Project 29 — Blockchain Application</v>
       </c>
       <c r="C30" t="str">
-        <v>Prakash Sharma, Mina Thapa, Tara Poudel</v>
+        <v>Kabita Joshi, Yubaraj Karki, Sarita Adhikari</v>
       </c>
       <c r="D30" t="str">
-        <v>078BCT085, 078BEI086, 078BCT087</v>
+        <v>81BCT088, 81BEI011, 81BCT057</v>
       </c>
       <c r="E30" t="str">
-        <v>2081</v>
+        <v>81</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
     <row r="31">
@@ -1094,22 +1103,22 @@
         <v>TestGroup_30</v>
       </c>
       <c r="B31" t="str">
-        <v>Test Bachelor Project 30 — Cloud Application</v>
+        <v>Test Bachelor Project 30 — Security Application</v>
       </c>
       <c r="C31" t="str">
-        <v>Reema Pokhrel, Sushma Adhikari, Anjana Bhandari</v>
+        <v>Nabin Bista, Reema Pathak, Anup Ghimire</v>
       </c>
       <c r="D31" t="str">
-        <v>078BEI088, 078BCT089, 078BEI090</v>
+        <v>81BCT091, 81BEI013, 81BCT062</v>
       </c>
       <c r="E31" t="str">
-        <v>2081</v>
+        <v>81</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>Assoc. Prof. Krishna Poudel</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
   </sheetData>
